--- a/r5-core-64-adding-related-person/ValueSet-at-core-vbpk.xlsx
+++ b/r5-core-64-adding-related-person/ValueSet-at-core-vbpk.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T17:05:56+00:00</t>
+    <t>2026-10-13T17:36:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
